--- a/FedMilLiPstET.xlsx
+++ b/FedMilLiPstET.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\FedGMil\csv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13906BFD-969E-4FE1-8425-90FCAD8C3AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9404CA-72B9-4188-8205-DDCFCCA770D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4C61A595-AF18-4592-83E7-997032580F64}"/>
   </bookViews>
@@ -25,9 +25,6 @@
     <t>LOGISTICS_ID</t>
   </si>
   <si>
-    <t>FEDERAL_ENTITY</t>
-  </si>
-  <si>
     <t>ORGANIZATIONAL_TIER</t>
   </si>
   <si>
@@ -137,6 +134,9 @@
   </si>
   <si>
     <t>Personnel Deployment Ledger</t>
+  </si>
+  <si>
+    <t>Agency</t>
   </si>
 </sst>
 </file>
@@ -693,7 +693,7 @@
   <autoFilter ref="A1:F11" xr:uid="{D46941AA-BEF2-477E-B27E-C45419D81505}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{4C0CFE9A-4E23-4288-BCC2-CC56AC5FF990}" name="LOGISTICS_ID"/>
-    <tableColumn id="2" xr3:uid="{BDD0D679-F753-4993-8F74-E1709C30CE37}" name="FEDERAL_ENTITY"/>
+    <tableColumn id="2" xr3:uid="{BDD0D679-F753-4993-8F74-E1709C30CE37}" name="Agency"/>
     <tableColumn id="3" xr3:uid="{DEC7469D-0DF1-4E21-8121-B94C5D694E09}" name="ORGANIZATIONAL_TIER"/>
     <tableColumn id="4" xr3:uid="{C1FD91D6-A5CB-4740-BC97-3C60EC6EB877}" name="DEFENSE_ASSET_CLASS"/>
     <tableColumn id="5" xr3:uid="{9951CAC7-1E61-4DF1-A3F1-6DC3792A57F2}" name="ALLOCATED_QUANTITY"/>
@@ -1036,33 +1036,33 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
       </c>
       <c r="E2">
         <v>27</v>
@@ -1073,16 +1073,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
       </c>
       <c r="E3">
         <v>44</v>
@@ -1093,16 +1093,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
         <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
       </c>
       <c r="E4">
         <v>61</v>
@@ -1113,16 +1113,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
       </c>
       <c r="E5">
         <v>78</v>
@@ -1133,16 +1133,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
         <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
       </c>
       <c r="E6">
         <v>95</v>
@@ -1153,16 +1153,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
       </c>
       <c r="E7">
         <v>112</v>
@@ -1173,16 +1173,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
         <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
       </c>
       <c r="E8">
         <v>129</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
         <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
       </c>
       <c r="E9">
         <v>146</v>
@@ -1213,16 +1213,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
         <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
       </c>
       <c r="E10">
         <v>163</v>
@@ -1233,16 +1233,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
       </c>
       <c r="E11">
         <v>180</v>
